--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O490"/>
+  <dimension ref="A1:O493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25442,6 +25442,159 @@
         <v>385.33</v>
       </c>
       <c r="O490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="C491" t="n">
+        <v>386.12</v>
+      </c>
+      <c r="D491" t="n">
+        <v>391.37</v>
+      </c>
+      <c r="E491" t="n">
+        <v>395.09</v>
+      </c>
+      <c r="F491" t="n">
+        <v>391.25</v>
+      </c>
+      <c r="G491" t="n">
+        <v>388.81</v>
+      </c>
+      <c r="H491" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="I491" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="J491" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="K491" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="L491" t="n">
+        <v>382.62</v>
+      </c>
+      <c r="M491" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="N491" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>389.54</v>
+      </c>
+      <c r="C492" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="D492" t="n">
+        <v>391.66</v>
+      </c>
+      <c r="E492" t="n">
+        <v>395.52</v>
+      </c>
+      <c r="F492" t="n">
+        <v>391.93</v>
+      </c>
+      <c r="G492" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="H492" t="n">
+        <v>389.63</v>
+      </c>
+      <c r="I492" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="J492" t="n">
+        <v>387.66</v>
+      </c>
+      <c r="K492" t="n">
+        <v>383.74</v>
+      </c>
+      <c r="L492" t="n">
+        <v>383.37</v>
+      </c>
+      <c r="M492" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="N492" t="n">
+        <v>384.53</v>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>389.07</v>
+      </c>
+      <c r="C493" t="n">
+        <v>386.72</v>
+      </c>
+      <c r="D493" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="E493" t="n">
+        <v>395.03</v>
+      </c>
+      <c r="F493" t="n">
+        <v>391.56</v>
+      </c>
+      <c r="G493" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="H493" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="I493" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="J493" t="n">
+        <v>387.65</v>
+      </c>
+      <c r="K493" t="n">
+        <v>384</v>
+      </c>
+      <c r="L493" t="n">
+        <v>383.87</v>
+      </c>
+      <c r="M493" t="n">
+        <v>389.69</v>
+      </c>
+      <c r="N493" t="n">
+        <v>384.22</v>
+      </c>
+      <c r="O493" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25458,7 +25611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30881,6 +31034,36 @@
       </c>
       <c r="B542" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -31049,28 +31232,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.40748512278599</v>
+        <v>0.3912530123276945</v>
       </c>
       <c r="J2" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K2" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2099425657335472</v>
+        <v>0.1938935069664297</v>
       </c>
       <c r="M2" t="n">
-        <v>4.818748916605746</v>
+        <v>4.86672219405347</v>
       </c>
       <c r="N2" t="n">
-        <v>37.21715991146861</v>
+        <v>38.17705527441517</v>
       </c>
       <c r="O2" t="n">
-        <v>6.100586849760325</v>
+        <v>6.178758392623487</v>
       </c>
       <c r="P2" t="n">
-        <v>392.3189165116783</v>
+        <v>392.4770982618045</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31127,28 +31310,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.319170089982315</v>
+        <v>0.3099189916433315</v>
       </c>
       <c r="J3" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K3" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1840200436666942</v>
+        <v>0.1751953687334591</v>
       </c>
       <c r="M3" t="n">
-        <v>4.02677832390197</v>
+        <v>4.051124685222224</v>
       </c>
       <c r="N3" t="n">
-        <v>26.90421245420146</v>
+        <v>27.12581120608177</v>
       </c>
       <c r="O3" t="n">
-        <v>5.186927072381244</v>
+        <v>5.208244541693657</v>
       </c>
       <c r="P3" t="n">
-        <v>386.1722577349781</v>
+        <v>386.2624091895273</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31205,28 +31388,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3994490503523822</v>
+        <v>0.3895557535194673</v>
       </c>
       <c r="J4" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K4" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2604853703884297</v>
+        <v>0.2503665179657805</v>
       </c>
       <c r="M4" t="n">
-        <v>3.88983616676928</v>
+        <v>3.913358479869425</v>
       </c>
       <c r="N4" t="n">
-        <v>26.98036179610333</v>
+        <v>27.25648555538427</v>
       </c>
       <c r="O4" t="n">
-        <v>5.194262391918927</v>
+        <v>5.220774421039878</v>
       </c>
       <c r="P4" t="n">
-        <v>389.4272379336551</v>
+        <v>389.5236493005964</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31283,28 +31466,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4033435021885287</v>
+        <v>0.3971967652828849</v>
       </c>
       <c r="J5" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K5" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2825109939569594</v>
+        <v>0.2775904892306349</v>
       </c>
       <c r="M5" t="n">
-        <v>3.739664365238425</v>
+        <v>3.748693257484351</v>
       </c>
       <c r="N5" t="n">
-        <v>24.60886465700383</v>
+        <v>24.62907852358591</v>
       </c>
       <c r="O5" t="n">
-        <v>4.960732270240336</v>
+        <v>4.962769239405143</v>
       </c>
       <c r="P5" t="n">
-        <v>389.9054033091016</v>
+        <v>389.9653039881136</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31361,28 +31544,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3928838445748674</v>
+        <v>0.3838239489247548</v>
       </c>
       <c r="J6" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K6" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2735562943630426</v>
+        <v>0.2640176104719641</v>
       </c>
       <c r="M6" t="n">
-        <v>3.857241878870264</v>
+        <v>3.878307396168885</v>
       </c>
       <c r="N6" t="n">
-        <v>24.41434881367161</v>
+        <v>24.63522595234088</v>
       </c>
       <c r="O6" t="n">
-        <v>4.941087816834631</v>
+        <v>4.963388555446861</v>
       </c>
       <c r="P6" t="n">
-        <v>389.0712317504569</v>
+        <v>389.1595205810962</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31439,28 +31622,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3266453745036241</v>
+        <v>0.3176332045381025</v>
       </c>
       <c r="J7" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K7" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2223276711446561</v>
+        <v>0.212272877213239</v>
       </c>
       <c r="M7" t="n">
-        <v>3.685147143484645</v>
+        <v>3.711755979223148</v>
       </c>
       <c r="N7" t="n">
-        <v>22.22888622305339</v>
+        <v>22.45902867638934</v>
       </c>
       <c r="O7" t="n">
-        <v>4.714751978954289</v>
+        <v>4.739095765690892</v>
       </c>
       <c r="P7" t="n">
-        <v>388.3162959074428</v>
+        <v>388.4041190805849</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31517,28 +31700,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3142285314336606</v>
+        <v>0.3048486495022205</v>
       </c>
       <c r="J8" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K8" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2228762351880141</v>
+        <v>0.2115500541689752</v>
       </c>
       <c r="M8" t="n">
-        <v>3.421246763042426</v>
+        <v>3.444283247611181</v>
       </c>
       <c r="N8" t="n">
-        <v>20.50591763753353</v>
+        <v>20.77721923332991</v>
       </c>
       <c r="O8" t="n">
-        <v>4.528346015658866</v>
+        <v>4.558203509424509</v>
       </c>
       <c r="P8" t="n">
-        <v>389.1437468065849</v>
+        <v>389.2351536436298</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31595,28 +31778,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2474425759915131</v>
+        <v>0.2378882671933301</v>
       </c>
       <c r="J9" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K9" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1312874573104248</v>
+        <v>0.1221590011440874</v>
       </c>
       <c r="M9" t="n">
-        <v>3.903794584619262</v>
+        <v>3.930236031549901</v>
       </c>
       <c r="N9" t="n">
-        <v>24.13033000890404</v>
+        <v>24.39463462778504</v>
       </c>
       <c r="O9" t="n">
-        <v>4.912263226752414</v>
+        <v>4.939092490304777</v>
       </c>
       <c r="P9" t="n">
-        <v>388.6826796015507</v>
+        <v>388.7757861902824</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31673,28 +31856,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1598099156951584</v>
+        <v>0.1508675743372741</v>
       </c>
       <c r="J10" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K10" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05836891577300385</v>
+        <v>0.05228079675131136</v>
       </c>
       <c r="M10" t="n">
-        <v>3.996001067245234</v>
+        <v>4.017689027386296</v>
       </c>
       <c r="N10" t="n">
-        <v>24.53963820035865</v>
+        <v>24.75068274129565</v>
       </c>
       <c r="O10" t="n">
-        <v>4.953749912980937</v>
+        <v>4.975005803141907</v>
       </c>
       <c r="P10" t="n">
-        <v>390.9210656890929</v>
+        <v>391.0082078495063</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31751,28 +31934,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08881445571980248</v>
+        <v>0.0809794971889783</v>
       </c>
       <c r="J11" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K11" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02120837167481515</v>
+        <v>0.01770301039062583</v>
       </c>
       <c r="M11" t="n">
-        <v>3.786508451631547</v>
+        <v>3.807240977104644</v>
       </c>
       <c r="N11" t="n">
-        <v>21.68262146343718</v>
+        <v>21.82748634639711</v>
       </c>
       <c r="O11" t="n">
-        <v>4.656460185960702</v>
+        <v>4.67198954904622</v>
       </c>
       <c r="P11" t="n">
-        <v>388.0628124570319</v>
+        <v>388.1391627460524</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31829,28 +32012,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1499349661962148</v>
+        <v>0.142265615764233</v>
       </c>
       <c r="J12" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K12" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05594023766098921</v>
+        <v>0.05071647567931215</v>
       </c>
       <c r="M12" t="n">
-        <v>3.88454953924604</v>
+        <v>3.90522053232121</v>
       </c>
       <c r="N12" t="n">
-        <v>22.59657319943701</v>
+        <v>22.72504005830771</v>
       </c>
       <c r="O12" t="n">
-        <v>4.753585299480489</v>
+        <v>4.767078776180199</v>
       </c>
       <c r="P12" t="n">
-        <v>385.9848177316977</v>
+        <v>386.0595534180011</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31907,28 +32090,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1288868181147294</v>
+        <v>0.1226454098517098</v>
       </c>
       <c r="J13" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K13" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03543041176736272</v>
+        <v>0.03239904004634686</v>
       </c>
       <c r="M13" t="n">
-        <v>4.180119612052187</v>
+        <v>4.182715910053624</v>
       </c>
       <c r="N13" t="n">
-        <v>26.93617469135416</v>
+        <v>26.94788158657193</v>
       </c>
       <c r="O13" t="n">
-        <v>5.190007195693871</v>
+        <v>5.191134903522729</v>
       </c>
       <c r="P13" t="n">
-        <v>391.2370122855113</v>
+        <v>391.2978332151158</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31985,28 +32168,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1811090415054919</v>
+        <v>0.176286749427536</v>
       </c>
       <c r="J14" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="K14" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05877662575058407</v>
+        <v>0.05638414979388096</v>
       </c>
       <c r="M14" t="n">
-        <v>4.540624437871117</v>
+        <v>4.540445149130212</v>
       </c>
       <c r="N14" t="n">
-        <v>31.28454679199683</v>
+        <v>31.19862222862035</v>
       </c>
       <c r="O14" t="n">
-        <v>5.593259049248196</v>
+        <v>5.585572685823752</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6839677549656</v>
+        <v>383.7309612145849</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32044,7 +32227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O490"/>
+  <dimension ref="A1:O493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69777,6 +69960,237 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-34.990539859237806,173.45958437163924</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-34.991095318771386,173.46012633444172</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-34.991478396385496,173.46081863793248</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-34.99172416382521,173.46161812211335</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-34.99203127338938,173.46242820591146</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-34.99231517551111,173.4632506733312</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-34.99255811910678,173.46408215191764</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-34.99276331146589,173.46492816576426</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-34.992922719192464,173.4657874179792</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-34.99304826722763,173.46665426093693</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-34.99310234754446,173.46753799253068</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-34.9930633766452,173.46838002347718</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>-34.99288084898811,173.46920181581925</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-34.99053290083268,173.45959429753677</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-34.99109049524049,173.46013193722766</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-34.99147614626215,173.46082025695648</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-34.99172058623102,173.46161993884434</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-34.992025567794144,173.46243093511222</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-34.99231128451181,173.46325241974836</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-34.992551999411056,173.46408443763647</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-34.992755778249986,173.464930402521</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-34.9929153490726,173.46578900067252</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-34.99304243282949,173.46665494144915</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-34.99309559043702,173.4675383336863</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-34.99306221853152,173.4683798029814</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>-34.99287700664902,173.4692002305617</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-34.990535649110434,173.45959037722452</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-34.99109140780039,173.46013087724117</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-34.99148041373741,173.46081718639365</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-34.99172466302439,173.461617868616</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-34.99202867230921,173.462429450106</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-34.99231136909875,173.46325238178278</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-34.9925544128122,173.46408353622627</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-34.99275893168922,173.46492946620427</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-34.99291543786923,173.4657889816039</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-34.993040099070235,173.46665521365398</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-34.99309108569874,173.46753856112338</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-34.99305651704868,173.46837871746362</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-34.99287965359373,173.46920132262798</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O493"/>
+  <dimension ref="A1:O496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25595,6 +25595,159 @@
         <v>384.22</v>
       </c>
       <c r="O493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>386.84</v>
+      </c>
+      <c r="C494" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="D494" t="n">
+        <v>390.53</v>
+      </c>
+      <c r="E494" t="n">
+        <v>394.21</v>
+      </c>
+      <c r="F494" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="G494" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="H494" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="I494" t="n">
+        <v>386.76</v>
+      </c>
+      <c r="J494" t="n">
+        <v>386.58</v>
+      </c>
+      <c r="K494" t="n">
+        <v>382.24</v>
+      </c>
+      <c r="L494" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="M494" t="n">
+        <v>387.97</v>
+      </c>
+      <c r="N494" t="n">
+        <v>381.17</v>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>388.02</v>
+      </c>
+      <c r="C495" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="D495" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="E495" t="n">
+        <v>394.73</v>
+      </c>
+      <c r="F495" t="n">
+        <v>391.57</v>
+      </c>
+      <c r="G495" t="n">
+        <v>388.68</v>
+      </c>
+      <c r="H495" t="n">
+        <v>389.29</v>
+      </c>
+      <c r="I495" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="J495" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="K495" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="L495" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="M495" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="N495" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="C496" t="n">
+        <v>385.81</v>
+      </c>
+      <c r="D496" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="E496" t="n">
+        <v>393.81</v>
+      </c>
+      <c r="F496" t="n">
+        <v>391.26</v>
+      </c>
+      <c r="G496" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="H496" t="n">
+        <v>388.96</v>
+      </c>
+      <c r="I496" t="n">
+        <v>387.88</v>
+      </c>
+      <c r="J496" t="n">
+        <v>387.42</v>
+      </c>
+      <c r="K496" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="L496" t="n">
+        <v>383.63</v>
+      </c>
+      <c r="M496" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="N496" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="O496" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25611,7 +25764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31064,6 +31217,36 @@
       </c>
       <c r="B545" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -31232,28 +31415,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3912530123276945</v>
+        <v>0.3742169231629712</v>
       </c>
       <c r="J2" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K2" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1938935069664297</v>
+        <v>0.1772149656967668</v>
       </c>
       <c r="M2" t="n">
-        <v>4.86672219405347</v>
+        <v>4.921060240467398</v>
       </c>
       <c r="N2" t="n">
-        <v>38.17705527441517</v>
+        <v>39.27778362244649</v>
       </c>
       <c r="O2" t="n">
-        <v>6.178758392623487</v>
+        <v>6.267199025278078</v>
       </c>
       <c r="P2" t="n">
-        <v>392.4770982618045</v>
+        <v>392.6438016085204</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31310,28 +31493,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3099189916433315</v>
+        <v>0.2999396714004369</v>
       </c>
       <c r="J3" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K3" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1751953687334591</v>
+        <v>0.1654307328202842</v>
       </c>
       <c r="M3" t="n">
-        <v>4.051124685222224</v>
+        <v>4.07914644029345</v>
       </c>
       <c r="N3" t="n">
-        <v>27.12581120608177</v>
+        <v>27.41751907765066</v>
       </c>
       <c r="O3" t="n">
-        <v>5.208244541693657</v>
+        <v>5.236174087790689</v>
       </c>
       <c r="P3" t="n">
-        <v>386.2624091895273</v>
+        <v>386.3600643765932</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31388,28 +31571,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3895557535194673</v>
+        <v>0.3794218225038594</v>
       </c>
       <c r="J4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2503665179657805</v>
+        <v>0.239854290162936</v>
       </c>
       <c r="M4" t="n">
-        <v>3.913358479869425</v>
+        <v>3.938459805745611</v>
       </c>
       <c r="N4" t="n">
-        <v>27.25648555538427</v>
+        <v>27.56183362221695</v>
       </c>
       <c r="O4" t="n">
-        <v>5.220774421039878</v>
+        <v>5.249936535065634</v>
       </c>
       <c r="P4" t="n">
-        <v>389.5236493005964</v>
+        <v>389.6228153990767</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31466,28 +31649,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3971967652828849</v>
+        <v>0.3900966758244584</v>
       </c>
       <c r="J5" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K5" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2775904892306349</v>
+        <v>0.2711460958492845</v>
       </c>
       <c r="M5" t="n">
-        <v>3.748693257484351</v>
+        <v>3.762425681686556</v>
       </c>
       <c r="N5" t="n">
-        <v>24.62907852358591</v>
+        <v>24.71130979499312</v>
       </c>
       <c r="O5" t="n">
-        <v>4.962769239405143</v>
+        <v>4.971047152762999</v>
       </c>
       <c r="P5" t="n">
-        <v>389.9653039881136</v>
+        <v>390.0347886948204</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31544,28 +31727,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3838239489247548</v>
+        <v>0.3747003873647393</v>
       </c>
       <c r="J6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2640176104719641</v>
+        <v>0.2543333035766984</v>
       </c>
       <c r="M6" t="n">
-        <v>3.878307396168885</v>
+        <v>3.900081290756627</v>
       </c>
       <c r="N6" t="n">
-        <v>24.63522595234088</v>
+        <v>24.86703100001396</v>
       </c>
       <c r="O6" t="n">
-        <v>4.963388555446861</v>
+        <v>4.986685372069704</v>
       </c>
       <c r="P6" t="n">
-        <v>389.1595205810962</v>
+        <v>389.248803192146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31622,28 +31805,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3176332045381025</v>
+        <v>0.3081809398278194</v>
       </c>
       <c r="J7" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K7" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.212272877213239</v>
+        <v>0.2015297247672206</v>
       </c>
       <c r="M7" t="n">
-        <v>3.711755979223148</v>
+        <v>3.740461987434873</v>
       </c>
       <c r="N7" t="n">
-        <v>22.45902867638934</v>
+        <v>22.73240209446542</v>
       </c>
       <c r="O7" t="n">
-        <v>4.739095765690892</v>
+        <v>4.76785088844706</v>
       </c>
       <c r="P7" t="n">
-        <v>388.4041190805849</v>
+        <v>388.4966146440661</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31700,28 +31883,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3048486495022205</v>
+        <v>0.2952987223031633</v>
       </c>
       <c r="J8" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K8" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2115500541689752</v>
+        <v>0.2000179348875162</v>
       </c>
       <c r="M8" t="n">
-        <v>3.444283247611181</v>
+        <v>3.468628888982489</v>
       </c>
       <c r="N8" t="n">
-        <v>20.77721923332991</v>
+        <v>21.06922614592408</v>
       </c>
       <c r="O8" t="n">
-        <v>4.558203509424509</v>
+        <v>4.590122672208672</v>
       </c>
       <c r="P8" t="n">
-        <v>389.2351536436298</v>
+        <v>389.3286070842573</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31778,28 +31961,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2378882671933301</v>
+        <v>0.2290486321064356</v>
       </c>
       <c r="J9" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K9" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221590011440874</v>
+        <v>0.11410779314848</v>
       </c>
       <c r="M9" t="n">
-        <v>3.930236031549901</v>
+        <v>3.952713624163782</v>
       </c>
       <c r="N9" t="n">
-        <v>24.39463462778504</v>
+        <v>24.60566559359997</v>
       </c>
       <c r="O9" t="n">
-        <v>4.939092490304777</v>
+        <v>4.96040982113373</v>
       </c>
       <c r="P9" t="n">
-        <v>388.7757861902824</v>
+        <v>388.8622839196865</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31856,28 +32039,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1508675743372741</v>
+        <v>0.1418702673373972</v>
       </c>
       <c r="J10" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K10" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05228079675131136</v>
+        <v>0.046429757887538</v>
       </c>
       <c r="M10" t="n">
-        <v>4.017689027386296</v>
+        <v>4.040735266217762</v>
       </c>
       <c r="N10" t="n">
-        <v>24.75068274129565</v>
+        <v>24.97199171801132</v>
       </c>
       <c r="O10" t="n">
-        <v>4.975005803141907</v>
+        <v>4.997198386897534</v>
       </c>
       <c r="P10" t="n">
-        <v>391.0082078495063</v>
+        <v>391.0962506467098</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31934,28 +32117,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0809794971889783</v>
+        <v>0.07233592485308837</v>
       </c>
       <c r="J11" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K11" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01770301039062583</v>
+        <v>0.01414053569379692</v>
       </c>
       <c r="M11" t="n">
-        <v>3.807240977104644</v>
+        <v>3.833283512283483</v>
       </c>
       <c r="N11" t="n">
-        <v>21.82748634639711</v>
+        <v>22.03795855740537</v>
       </c>
       <c r="O11" t="n">
-        <v>4.67198954904622</v>
+        <v>4.694460411741201</v>
       </c>
       <c r="P11" t="n">
-        <v>388.1391627460524</v>
+        <v>388.2237430780211</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32012,28 +32195,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.142265615764233</v>
+        <v>0.1348598268759102</v>
       </c>
       <c r="J12" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K12" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05071647567931215</v>
+        <v>0.04589876928073544</v>
       </c>
       <c r="M12" t="n">
-        <v>3.90522053232121</v>
+        <v>3.923976789576057</v>
       </c>
       <c r="N12" t="n">
-        <v>22.72504005830771</v>
+        <v>22.83877197175125</v>
       </c>
       <c r="O12" t="n">
-        <v>4.767078776180199</v>
+        <v>4.778992777955545</v>
       </c>
       <c r="P12" t="n">
-        <v>386.0595534180011</v>
+        <v>386.1320223722688</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32090,28 +32273,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1226454098517098</v>
+        <v>0.115184467585821</v>
       </c>
       <c r="J13" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K13" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03239904004634686</v>
+        <v>0.02878859333971973</v>
       </c>
       <c r="M13" t="n">
-        <v>4.182715910053624</v>
+        <v>4.191358311636534</v>
       </c>
       <c r="N13" t="n">
-        <v>26.94788158657193</v>
+        <v>27.03929134109083</v>
       </c>
       <c r="O13" t="n">
-        <v>5.191134903522729</v>
+        <v>5.199931859273814</v>
       </c>
       <c r="P13" t="n">
-        <v>391.2978332151158</v>
+        <v>391.3708462891554</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32168,28 +32351,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.176286749427536</v>
+        <v>0.1680458780095218</v>
       </c>
       <c r="J14" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K14" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05638414979388096</v>
+        <v>0.05165451445609259</v>
       </c>
       <c r="M14" t="n">
-        <v>4.540445149130212</v>
+        <v>4.559413833637342</v>
       </c>
       <c r="N14" t="n">
-        <v>31.19862222862035</v>
+        <v>31.32046225797757</v>
       </c>
       <c r="O14" t="n">
-        <v>5.585572685823752</v>
+        <v>5.59646873108191</v>
       </c>
       <c r="P14" t="n">
-        <v>383.7309612145849</v>
+        <v>383.8116080369986</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32227,7 +32410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O493"/>
+  <dimension ref="A1:O496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70191,6 +70374,237 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-34.99054868880953,173.45957177659042</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-34.991100337850554,173.46012050451512</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-34.991484913983975,173.46081394834525</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-34.99173148541322,173.46161440415182</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-34.99203253197656,173.46242760388182</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-34.99232151953165,173.46324782591157</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-34.99256156682265,173.46408086418862</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-34.992760771195435,173.4649289200195</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-34.99292493910808,173.46578694126427</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-34.99305589682518,173.46665337103622</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-34.993099284322426,173.46753814718792</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-34.99307183978374,173.46838163479293</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>-34.992905696113716,173.4692120671549</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-34.99054178887942,173.45958161907913</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-34.991096361696954,173.46012512302846</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-34.99148111205154,173.4608166839379</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-34.99172715902032,173.46161660112915</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-34.992028588403386,173.46242949024128</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-34.99231627514134,173.46325017977853</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-34.99255492996957,173.46408334306693</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-34.992755953441055,173.4649303505034</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-34.99291827936123,173.46578837140893</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-34.993051678106546,173.46665386309897</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-34.993095500342264,173.46753833823504</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-34.993070770755715,173.46838143125828</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-34.992903817636915,173.4692112921396</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-34.99053728638222,173.4595880417192</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-34.991097339439655,173.46012398732853</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-34.99147909469962,173.46081813547676</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-34.99173481340774,173.46161271416906</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-34.99203118948357,173.46242824604678</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-34.99231526009804,173.46325063536563</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-34.99255777433518,173.46408228069055</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-34.9927509604956,173.46493183300475</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-34.99291748019159,173.4657885430263</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-34.993047728667804,173.46665432375343</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-34.99309324797312,173.46753845195357</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>-34.99307219612641,173.4683817026378</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>-34.99290765997585,173.46921287739818</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O496"/>
+  <dimension ref="A1:O497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25750,6 +25750,57 @@
       <c r="O496" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="C497" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="D497" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="E497" t="n">
+        <v>395.14</v>
+      </c>
+      <c r="F497" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="G497" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="H497" t="n">
+        <v>391.19</v>
+      </c>
+      <c r="I497" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="J497" t="n">
+        <v>390.81</v>
+      </c>
+      <c r="K497" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="L497" t="n">
+        <v>387.68</v>
+      </c>
+      <c r="M497" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="N497" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B548"/>
+  <dimension ref="A1:B549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31247,6 +31298,16 @@
       </c>
       <c r="B548" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -31415,28 +31476,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3742169231629712</v>
+        <v>0.3705920165579429</v>
       </c>
       <c r="J2" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1772149656967668</v>
+        <v>0.1743696545728337</v>
       </c>
       <c r="M2" t="n">
-        <v>4.921060240467398</v>
+        <v>4.929174150592995</v>
       </c>
       <c r="N2" t="n">
-        <v>39.27778362244649</v>
+        <v>39.37858935209862</v>
       </c>
       <c r="O2" t="n">
-        <v>6.267199025278078</v>
+        <v>6.275236198909059</v>
       </c>
       <c r="P2" t="n">
-        <v>392.6438016085204</v>
+        <v>392.679520913488</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31493,28 +31554,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2999396714004369</v>
+        <v>0.2977052340295776</v>
       </c>
       <c r="J3" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K3" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1654307328202842</v>
+        <v>0.163638167012059</v>
       </c>
       <c r="M3" t="n">
-        <v>4.07914644029345</v>
+        <v>4.082638221877289</v>
       </c>
       <c r="N3" t="n">
-        <v>27.41751907765066</v>
+        <v>27.43063341312162</v>
       </c>
       <c r="O3" t="n">
-        <v>5.236174087790689</v>
+        <v>5.237426220303405</v>
       </c>
       <c r="P3" t="n">
-        <v>386.3600643765932</v>
+        <v>386.3820821990026</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31571,28 +31632,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3794218225038594</v>
+        <v>0.3767533785927996</v>
       </c>
       <c r="J4" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.239854290162936</v>
+        <v>0.2374478331105873</v>
       </c>
       <c r="M4" t="n">
-        <v>3.938459805745611</v>
+        <v>3.943313066671725</v>
       </c>
       <c r="N4" t="n">
-        <v>27.56183362221695</v>
+        <v>27.60380535190865</v>
       </c>
       <c r="O4" t="n">
-        <v>5.249936535065634</v>
+        <v>5.253932370321173</v>
       </c>
       <c r="P4" t="n">
-        <v>389.6228153990767</v>
+        <v>389.6491098591094</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31649,28 +31710,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3900966758244584</v>
+        <v>0.3880786926594563</v>
       </c>
       <c r="J5" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K5" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2711460958492845</v>
+        <v>0.2695243957024952</v>
       </c>
       <c r="M5" t="n">
-        <v>3.762425681686556</v>
+        <v>3.765345985570049</v>
       </c>
       <c r="N5" t="n">
-        <v>24.71130979499312</v>
+        <v>24.71727154800783</v>
       </c>
       <c r="O5" t="n">
-        <v>4.971047152762999</v>
+        <v>4.971646764202766</v>
       </c>
       <c r="P5" t="n">
-        <v>390.0347886948204</v>
+        <v>390.054673608818</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31727,28 +31788,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3747003873647393</v>
+        <v>0.3726195355238239</v>
       </c>
       <c r="J6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2543333035766984</v>
+        <v>0.2526087345033597</v>
       </c>
       <c r="M6" t="n">
-        <v>3.900081290756627</v>
+        <v>3.902531480700996</v>
       </c>
       <c r="N6" t="n">
-        <v>24.86703100001396</v>
+        <v>24.87620868831138</v>
       </c>
       <c r="O6" t="n">
-        <v>4.986685372069704</v>
+        <v>4.987605506484187</v>
       </c>
       <c r="P6" t="n">
-        <v>389.248803192146</v>
+        <v>389.2693076049755</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31805,28 +31866,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3081809398278194</v>
+        <v>0.306079760002605</v>
       </c>
       <c r="J7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2015297247672206</v>
+        <v>0.1996161935973111</v>
       </c>
       <c r="M7" t="n">
-        <v>3.740461987434873</v>
+        <v>3.744173270285799</v>
       </c>
       <c r="N7" t="n">
-        <v>22.73240209446542</v>
+        <v>22.74704799280851</v>
       </c>
       <c r="O7" t="n">
-        <v>4.76785088844706</v>
+        <v>4.769386542607813</v>
       </c>
       <c r="P7" t="n">
-        <v>388.4966146440661</v>
+        <v>388.5173193659104</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31883,28 +31944,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2952987223031633</v>
+        <v>0.2930061439151885</v>
       </c>
       <c r="J8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2000179348875162</v>
+        <v>0.1976927874589356</v>
       </c>
       <c r="M8" t="n">
-        <v>3.468628888982489</v>
+        <v>3.472319675081632</v>
       </c>
       <c r="N8" t="n">
-        <v>21.06922614592408</v>
+        <v>21.09874492147217</v>
       </c>
       <c r="O8" t="n">
-        <v>4.590122672208672</v>
+        <v>4.593337013704978</v>
       </c>
       <c r="P8" t="n">
-        <v>389.3286070842573</v>
+        <v>389.3511978198333</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31961,28 +32022,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2290486321064356</v>
+        <v>0.2274204403703181</v>
       </c>
       <c r="J9" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K9" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L9" t="n">
-        <v>0.11410779314848</v>
+        <v>0.1129670129475191</v>
       </c>
       <c r="M9" t="n">
-        <v>3.952713624163782</v>
+        <v>3.953171613953035</v>
       </c>
       <c r="N9" t="n">
-        <v>24.60566559359997</v>
+        <v>24.59237167625323</v>
       </c>
       <c r="O9" t="n">
-        <v>4.96040982113373</v>
+        <v>4.959069638173397</v>
       </c>
       <c r="P9" t="n">
-        <v>388.8622839196865</v>
+        <v>388.8783278853675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32039,28 +32100,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1418702673373972</v>
+        <v>0.1403155045725271</v>
       </c>
       <c r="J10" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K10" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L10" t="n">
-        <v>0.046429757887538</v>
+        <v>0.04559768041296786</v>
       </c>
       <c r="M10" t="n">
-        <v>4.040735266217762</v>
+        <v>4.040863724998816</v>
       </c>
       <c r="N10" t="n">
-        <v>24.97199171801132</v>
+        <v>24.95475766100193</v>
       </c>
       <c r="O10" t="n">
-        <v>4.997198386897534</v>
+        <v>4.995473717376755</v>
       </c>
       <c r="P10" t="n">
-        <v>391.0962506467098</v>
+        <v>391.1115710539373</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32117,28 +32178,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07233592485308837</v>
+        <v>0.07106680339211083</v>
       </c>
       <c r="J11" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K11" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01414053569379692</v>
+        <v>0.01370139966825945</v>
       </c>
       <c r="M11" t="n">
-        <v>3.833283512283483</v>
+        <v>3.832728853755969</v>
       </c>
       <c r="N11" t="n">
-        <v>22.03795855740537</v>
+        <v>22.01559060337789</v>
       </c>
       <c r="O11" t="n">
-        <v>4.694460411741201</v>
+        <v>4.692077429388595</v>
       </c>
       <c r="P11" t="n">
-        <v>388.2237430780211</v>
+        <v>388.2362488171877</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32195,28 +32256,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1348598268759102</v>
+        <v>0.1340778354536219</v>
       </c>
       <c r="J12" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K12" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04589876928073544</v>
+        <v>0.04556764447414463</v>
       </c>
       <c r="M12" t="n">
-        <v>3.923976789576057</v>
+        <v>3.920485592951657</v>
       </c>
       <c r="N12" t="n">
-        <v>22.83877197175125</v>
+        <v>22.80110270950235</v>
       </c>
       <c r="O12" t="n">
-        <v>4.778992777955545</v>
+        <v>4.775050021675412</v>
       </c>
       <c r="P12" t="n">
-        <v>386.1320223722688</v>
+        <v>386.1397280025479</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32273,28 +32334,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.115184467585821</v>
+        <v>0.1136649981549239</v>
       </c>
       <c r="J13" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K13" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02878859333971973</v>
+        <v>0.02814370812569966</v>
       </c>
       <c r="M13" t="n">
-        <v>4.191358311636534</v>
+        <v>4.18980774199933</v>
       </c>
       <c r="N13" t="n">
-        <v>27.03929134109083</v>
+        <v>27.01640307820897</v>
       </c>
       <c r="O13" t="n">
-        <v>5.199931859273814</v>
+        <v>5.197730569990038</v>
       </c>
       <c r="P13" t="n">
-        <v>391.3708462891554</v>
+        <v>391.3858189209787</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32351,28 +32412,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1680458780095218</v>
+        <v>0.1658595347728244</v>
       </c>
       <c r="J14" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K14" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05165451445609259</v>
+        <v>0.05049748942573051</v>
       </c>
       <c r="M14" t="n">
-        <v>4.559413833637342</v>
+        <v>4.562374632197004</v>
       </c>
       <c r="N14" t="n">
-        <v>31.32046225797757</v>
+        <v>31.32279531354483</v>
       </c>
       <c r="O14" t="n">
-        <v>5.59646873108191</v>
+        <v>5.596677167172038</v>
       </c>
       <c r="P14" t="n">
-        <v>383.8116080369986</v>
+        <v>383.8331519467718</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32410,7 +32471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O496"/>
+  <dimension ref="A1:O497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70605,6 +70666,83 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-34.99051196713845,173.45962415863002</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-34.991079805252184,173.46014435421037</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-34.99146776649232,173.46082628642438</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-34.99172374782588,173.46161833336114</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-34.99201004521853,173.46243836014187</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-34.99229495923187,173.46325974710552</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-34.99253855331891,173.46408945977802</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-34.99272625855462,173.4649391674825</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-34.99288737813552,173.4657950072772</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-34.99301469699821,173.46665817649824</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>-34.99305675959286,173.46754029419293</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>-34.99304965745213,173.4683774114503</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-34.99289374217026,173.46920713524005</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O497"/>
+  <dimension ref="A1:O500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25801,6 +25801,159 @@
       <c r="O497" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>394.97</v>
+      </c>
+      <c r="C498" t="n">
+        <v>389.5</v>
+      </c>
+      <c r="D498" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="E498" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="F498" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="G498" t="n">
+        <v>392.06</v>
+      </c>
+      <c r="H498" t="n">
+        <v>392.32</v>
+      </c>
+      <c r="I498" t="n">
+        <v>391.59</v>
+      </c>
+      <c r="J498" t="n">
+        <v>390.81</v>
+      </c>
+      <c r="K498" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="L498" t="n">
+        <v>387.68</v>
+      </c>
+      <c r="M498" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="N498" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="C499" t="n">
+        <v>389.83</v>
+      </c>
+      <c r="D499" t="n">
+        <v>393.49</v>
+      </c>
+      <c r="E499" t="n">
+        <v>395.16</v>
+      </c>
+      <c r="F499" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="G499" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="H499" t="n">
+        <v>391.71</v>
+      </c>
+      <c r="I499" t="n">
+        <v>390.69</v>
+      </c>
+      <c r="J499" t="n">
+        <v>390.68</v>
+      </c>
+      <c r="K499" t="n">
+        <v>386.77</v>
+      </c>
+      <c r="L499" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="M499" t="n">
+        <v>391.35</v>
+      </c>
+      <c r="N499" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>397.73</v>
+      </c>
+      <c r="C500" t="n">
+        <v>390.38</v>
+      </c>
+      <c r="D500" t="n">
+        <v>393.84</v>
+      </c>
+      <c r="E500" t="n">
+        <v>395.51</v>
+      </c>
+      <c r="F500" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="G500" t="n">
+        <v>392.64</v>
+      </c>
+      <c r="H500" t="n">
+        <v>392.81</v>
+      </c>
+      <c r="I500" t="n">
+        <v>391.48</v>
+      </c>
+      <c r="J500" t="n">
+        <v>391.44</v>
+      </c>
+      <c r="K500" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="L500" t="n">
+        <v>386.32</v>
+      </c>
+      <c r="M500" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="N500" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25815,7 +25968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B549"/>
+  <dimension ref="A1:B552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31308,6 +31461,36 @@
       </c>
       <c r="B549" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -31476,28 +31659,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3705920165579429</v>
+        <v>0.3632635969561758</v>
       </c>
       <c r="J2" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1743696545728337</v>
+        <v>0.1696339820852109</v>
       </c>
       <c r="M2" t="n">
-        <v>4.929174150592995</v>
+        <v>4.935633642571137</v>
       </c>
       <c r="N2" t="n">
-        <v>39.37858935209862</v>
+        <v>39.39701322077552</v>
       </c>
       <c r="O2" t="n">
-        <v>6.275236198909059</v>
+        <v>6.276704009332885</v>
       </c>
       <c r="P2" t="n">
-        <v>392.679520913488</v>
+        <v>392.7519741366141</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31554,28 +31737,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2977052340295776</v>
+        <v>0.2926927537919592</v>
       </c>
       <c r="J3" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.163638167012059</v>
+        <v>0.1602421773225486</v>
       </c>
       <c r="M3" t="n">
-        <v>4.082638221877289</v>
+        <v>4.084096764664617</v>
       </c>
       <c r="N3" t="n">
-        <v>27.43063341312162</v>
+        <v>27.38192596929381</v>
       </c>
       <c r="O3" t="n">
-        <v>5.237426220303405</v>
+        <v>5.232774213483113</v>
       </c>
       <c r="P3" t="n">
-        <v>386.3820821990026</v>
+        <v>386.4316472514995</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31632,28 +31815,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3767533785927996</v>
+        <v>0.3699188304088373</v>
       </c>
       <c r="J4" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K4" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2374478331105873</v>
+        <v>0.2318416209686283</v>
       </c>
       <c r="M4" t="n">
-        <v>3.943313066671725</v>
+        <v>3.952880827942894</v>
       </c>
       <c r="N4" t="n">
-        <v>27.60380535190865</v>
+        <v>27.65254297102212</v>
       </c>
       <c r="O4" t="n">
-        <v>5.253932370321173</v>
+        <v>5.258568528698863</v>
       </c>
       <c r="P4" t="n">
-        <v>389.6491098591094</v>
+        <v>389.7166994935477</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31710,28 +31893,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3880786926594563</v>
+        <v>0.3824743672831932</v>
       </c>
       <c r="J5" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K5" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2695243957024952</v>
+        <v>0.265259586100836</v>
       </c>
       <c r="M5" t="n">
-        <v>3.765345985570049</v>
+        <v>3.771726574877289</v>
       </c>
       <c r="N5" t="n">
-        <v>24.71727154800783</v>
+        <v>24.71327719315365</v>
       </c>
       <c r="O5" t="n">
-        <v>4.971646764202766</v>
+        <v>4.971245034511339</v>
       </c>
       <c r="P5" t="n">
-        <v>390.054673608818</v>
+        <v>390.1100989960938</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31788,28 +31971,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3726195355238239</v>
+        <v>0.366693771010444</v>
       </c>
       <c r="J6" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2526087345033597</v>
+        <v>0.247842773736179</v>
       </c>
       <c r="M6" t="n">
-        <v>3.902531480700996</v>
+        <v>3.908281790611418</v>
       </c>
       <c r="N6" t="n">
-        <v>24.87620868831138</v>
+        <v>24.88870307757516</v>
       </c>
       <c r="O6" t="n">
-        <v>4.987605506484187</v>
+        <v>4.988857893102905</v>
       </c>
       <c r="P6" t="n">
-        <v>389.2693076049755</v>
+        <v>389.3279155275606</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31866,28 +32049,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.306079760002605</v>
+        <v>0.3008262220283059</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1996161935973111</v>
+        <v>0.1953230843774348</v>
       </c>
       <c r="M7" t="n">
-        <v>3.744173270285799</v>
+        <v>3.749644016819844</v>
       </c>
       <c r="N7" t="n">
-        <v>22.74704799280851</v>
+        <v>22.73851915197169</v>
       </c>
       <c r="O7" t="n">
-        <v>4.769386542607813</v>
+        <v>4.768492335316446</v>
       </c>
       <c r="P7" t="n">
-        <v>388.5173193659104</v>
+        <v>388.5692684139345</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31944,28 +32127,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2930061439151885</v>
+        <v>0.2874626404838804</v>
       </c>
       <c r="J8" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K8" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1976927874589356</v>
+        <v>0.1927008256925251</v>
       </c>
       <c r="M8" t="n">
-        <v>3.472319675081632</v>
+        <v>3.477275927208264</v>
       </c>
       <c r="N8" t="n">
-        <v>21.09874492147217</v>
+        <v>21.11429492161067</v>
       </c>
       <c r="O8" t="n">
-        <v>4.593337013704978</v>
+        <v>4.595029371136889</v>
       </c>
       <c r="P8" t="n">
-        <v>389.3511978198333</v>
+        <v>389.4060153123883</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32022,28 +32205,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2274204403703181</v>
+        <v>0.2232340571218459</v>
       </c>
       <c r="J9" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K9" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1129670129475191</v>
+        <v>0.1102604427531096</v>
       </c>
       <c r="M9" t="n">
-        <v>3.953171613953035</v>
+        <v>3.950825729844428</v>
       </c>
       <c r="N9" t="n">
-        <v>24.59237167625323</v>
+        <v>24.52601004395244</v>
       </c>
       <c r="O9" t="n">
-        <v>4.959069638173397</v>
+        <v>4.952374182546431</v>
       </c>
       <c r="P9" t="n">
-        <v>388.8783278853675</v>
+        <v>388.9197283406027</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32100,28 +32283,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1403155045725271</v>
+        <v>0.1359190852979021</v>
       </c>
       <c r="J10" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K10" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04559768041296786</v>
+        <v>0.04330128460665805</v>
       </c>
       <c r="M10" t="n">
-        <v>4.040863724998816</v>
+        <v>4.039795794094311</v>
       </c>
       <c r="N10" t="n">
-        <v>24.95475766100193</v>
+        <v>24.89419724448799</v>
       </c>
       <c r="O10" t="n">
-        <v>4.995473717376755</v>
+        <v>4.989408506475291</v>
       </c>
       <c r="P10" t="n">
-        <v>391.1115710539373</v>
+        <v>391.1550442803195</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32178,28 +32361,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07106680339211083</v>
+        <v>0.067638812557459</v>
       </c>
       <c r="J11" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K11" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01370139966825945</v>
+        <v>0.01255917524082473</v>
       </c>
       <c r="M11" t="n">
-        <v>3.832728853755969</v>
+        <v>3.828904608826419</v>
       </c>
       <c r="N11" t="n">
-        <v>22.01559060337789</v>
+        <v>21.93838923458436</v>
       </c>
       <c r="O11" t="n">
-        <v>4.692077429388595</v>
+        <v>4.683843425498376</v>
       </c>
       <c r="P11" t="n">
-        <v>388.2362488171877</v>
+        <v>388.270142472684</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32256,28 +32439,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1340778354536219</v>
+        <v>0.131073898601358</v>
       </c>
       <c r="J12" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K12" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04556764447414463</v>
+        <v>0.0441099938506625</v>
       </c>
       <c r="M12" t="n">
-        <v>3.920485592951657</v>
+        <v>3.91397717445602</v>
       </c>
       <c r="N12" t="n">
-        <v>22.80110270950235</v>
+        <v>22.70733607751702</v>
       </c>
       <c r="O12" t="n">
-        <v>4.775050021675412</v>
+        <v>4.765221514002998</v>
       </c>
       <c r="P12" t="n">
-        <v>386.1397280025479</v>
+        <v>386.1694464920175</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32334,28 +32517,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1136649981549239</v>
+        <v>0.1093662703990876</v>
       </c>
       <c r="J13" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K13" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02814370812569966</v>
+        <v>0.02636446829259165</v>
       </c>
       <c r="M13" t="n">
-        <v>4.18980774199933</v>
+        <v>4.184101815766855</v>
       </c>
       <c r="N13" t="n">
-        <v>27.01640307820897</v>
+        <v>26.94058558696912</v>
       </c>
       <c r="O13" t="n">
-        <v>5.197730569990038</v>
+        <v>5.190432119483803</v>
       </c>
       <c r="P13" t="n">
-        <v>391.3858189209787</v>
+        <v>391.4283377566949</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32412,28 +32595,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1658595347728244</v>
+        <v>0.1605013183654403</v>
       </c>
       <c r="J14" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K14" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05049748942573051</v>
+        <v>0.04784229599364886</v>
       </c>
       <c r="M14" t="n">
-        <v>4.562374632197004</v>
+        <v>4.564538693536386</v>
       </c>
       <c r="N14" t="n">
-        <v>31.32279531354483</v>
+        <v>31.26921005430147</v>
       </c>
       <c r="O14" t="n">
-        <v>5.596677167172038</v>
+        <v>5.59188787926774</v>
       </c>
       <c r="P14" t="n">
-        <v>383.8331519467718</v>
+        <v>383.886133727562</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32471,7 +32654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O497"/>
+  <dimension ref="A1:O500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70743,6 +70926,237 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-34.99050114944444,173.45963958963594</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-34.991073286966,173.46015192553972</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-34.99146039539823,173.46083159012198</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-34.99171883903385,173.46162082608498</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-34.992004087905606,173.4624412097471</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-34.99228768475464,173.4632630121446</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-34.99252881352123,173.46409309761032</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-34.99271846255186,173.46494148226355</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-34.99288737813552,173.4657950072772</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-34.99301469699821,173.46665817649824</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-34.99305675959286,173.46754029419293</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-34.99304965745213,173.4683774114503</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-34.99289374217026,173.46920713524005</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-34.99049746558063,173.4596448445181</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-34.99107113593147,173.46015442407813</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-34.99146194720754,173.46083047355415</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-34.991723581426164,173.46161841786028</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-34.99201080037087,173.4624379989243</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-34.99229284455826,173.46326069624484</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-34.99253407128814,173.46409113382484</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-34.99272634615015,173.4649391414737</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-34.992888532491655,173.46579475938566</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-34.99301523555804,173.46665811368177</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-34.993060994046886,173.46754008040224</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-34.99304172882753,173.4683759019027</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-34.992881702841245,173.4692021680987</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-34.990485010610826,173.45966261102097</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-34.99106755087379,173.46015858830853</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-34.99145923154124,173.4608324275478</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-34.99172066943089,173.46161989659478</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-34.99201004521853,173.46243836014187</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-34.99228277871182,173.46326521414736</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-34.99252459006912,173.46409467507715</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-34.99271942610276,173.46494119616708</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-34.99288178394805,173.46579620859765</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-34.99300670836069,173.46665910827573</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-34.99306901248107,173.46753967556455</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>-34.993053220878906,173.46837808989875</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>-34.99288110514405,173.46920192150307</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O500"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25952,6 +25952,210 @@
         <v>384.05</v>
       </c>
       <c r="O500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>397.48</v>
+      </c>
+      <c r="C501" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="D501" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="E501" t="n">
+        <v>395.41</v>
+      </c>
+      <c r="F501" t="n">
+        <v>393.85</v>
+      </c>
+      <c r="G501" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="H501" t="n">
+        <v>392.79</v>
+      </c>
+      <c r="I501" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="J501" t="n">
+        <v>391.38</v>
+      </c>
+      <c r="K501" t="n">
+        <v>387.63</v>
+      </c>
+      <c r="L501" t="n">
+        <v>386.52</v>
+      </c>
+      <c r="M501" t="n">
+        <v>390.39</v>
+      </c>
+      <c r="N501" t="n">
+        <v>384.21</v>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>397.61</v>
+      </c>
+      <c r="C502" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="D502" t="n">
+        <v>394.01</v>
+      </c>
+      <c r="E502" t="n">
+        <v>395.74</v>
+      </c>
+      <c r="F502" t="n">
+        <v>393.86</v>
+      </c>
+      <c r="G502" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="H502" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="I502" t="n">
+        <v>391.16</v>
+      </c>
+      <c r="J502" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="K502" t="n">
+        <v>387.34</v>
+      </c>
+      <c r="L502" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="M502" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="N502" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>400.41</v>
+      </c>
+      <c r="C503" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="D503" t="n">
+        <v>394.08</v>
+      </c>
+      <c r="E503" t="n">
+        <v>395.98</v>
+      </c>
+      <c r="F503" t="n">
+        <v>395.19</v>
+      </c>
+      <c r="G503" t="n">
+        <v>393.02</v>
+      </c>
+      <c r="H503" t="n">
+        <v>393.75</v>
+      </c>
+      <c r="I503" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="J503" t="n">
+        <v>391.92</v>
+      </c>
+      <c r="K503" t="n">
+        <v>387.35</v>
+      </c>
+      <c r="L503" t="n">
+        <v>386.63</v>
+      </c>
+      <c r="M503" t="n">
+        <v>390.07</v>
+      </c>
+      <c r="N503" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>400.58</v>
+      </c>
+      <c r="C504" t="n">
+        <v>391.85</v>
+      </c>
+      <c r="D504" t="n">
+        <v>394.8</v>
+      </c>
+      <c r="E504" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="F504" t="n">
+        <v>395.71</v>
+      </c>
+      <c r="G504" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="H504" t="n">
+        <v>393.86</v>
+      </c>
+      <c r="I504" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="J504" t="n">
+        <v>391.76</v>
+      </c>
+      <c r="K504" t="n">
+        <v>387.38</v>
+      </c>
+      <c r="L504" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="M504" t="n">
+        <v>389.81</v>
+      </c>
+      <c r="N504" t="n">
+        <v>384.71</v>
+      </c>
+      <c r="O504" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25968,7 +26172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B552"/>
+  <dimension ref="A1:B556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31491,6 +31695,46 @@
       </c>
       <c r="B552" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -31659,28 +31903,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3632635969561758</v>
+        <v>0.3581312927732338</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1696339820852109</v>
+        <v>0.1676824999327913</v>
       </c>
       <c r="M2" t="n">
-        <v>4.935633642571137</v>
+        <v>4.921494360587817</v>
       </c>
       <c r="N2" t="n">
-        <v>39.39701322077552</v>
+        <v>39.19366941961626</v>
       </c>
       <c r="O2" t="n">
-        <v>6.276704009332885</v>
+        <v>6.260484759155338</v>
       </c>
       <c r="P2" t="n">
-        <v>392.7519741366141</v>
+        <v>392.8029259480419</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31737,28 +31981,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2926927537919592</v>
+        <v>0.2880601019176976</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1602421773225486</v>
+        <v>0.1579045148375373</v>
       </c>
       <c r="M3" t="n">
-        <v>4.084096764664617</v>
+        <v>4.075777390681898</v>
       </c>
       <c r="N3" t="n">
-        <v>27.38192596929381</v>
+        <v>27.24351309013733</v>
       </c>
       <c r="O3" t="n">
-        <v>5.232774213483113</v>
+        <v>5.219531884195875</v>
       </c>
       <c r="P3" t="n">
-        <v>386.4316472514995</v>
+        <v>386.4776464697645</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31815,28 +32059,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3699188304088373</v>
+        <v>0.3618901110296921</v>
       </c>
       <c r="J4" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2318416209686283</v>
+        <v>0.2257016338868255</v>
       </c>
       <c r="M4" t="n">
-        <v>3.952880827942894</v>
+        <v>3.960839127732184</v>
       </c>
       <c r="N4" t="n">
-        <v>27.65254297102212</v>
+        <v>27.66031807085589</v>
       </c>
       <c r="O4" t="n">
-        <v>5.258568528698863</v>
+        <v>5.25930775586064</v>
       </c>
       <c r="P4" t="n">
-        <v>389.7166994935477</v>
+        <v>389.7964297460388</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31893,28 +32137,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3824743672831932</v>
+        <v>0.3757831403514046</v>
       </c>
       <c r="J5" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.265259586100836</v>
+        <v>0.2605344338992297</v>
       </c>
       <c r="M5" t="n">
-        <v>3.771726574877289</v>
+        <v>3.776762291923007</v>
       </c>
       <c r="N5" t="n">
-        <v>24.71327719315365</v>
+        <v>24.67501959251341</v>
       </c>
       <c r="O5" t="n">
-        <v>4.971245034511339</v>
+        <v>4.967395654919528</v>
       </c>
       <c r="P5" t="n">
-        <v>390.1100989960938</v>
+        <v>390.1765466529969</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31971,28 +32215,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.366693771010444</v>
+        <v>0.3600223274584813</v>
       </c>
       <c r="J6" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.247842773736179</v>
+        <v>0.2430445626259837</v>
       </c>
       <c r="M6" t="n">
-        <v>3.908281790611418</v>
+        <v>3.909881473854861</v>
       </c>
       <c r="N6" t="n">
-        <v>24.88870307757516</v>
+        <v>24.85268825824873</v>
       </c>
       <c r="O6" t="n">
-        <v>4.988857893102905</v>
+        <v>4.985247060903675</v>
       </c>
       <c r="P6" t="n">
-        <v>389.3279155275606</v>
+        <v>389.3941600739424</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32049,28 +32293,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3008262220283059</v>
+        <v>0.2951840695622887</v>
       </c>
       <c r="J7" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K7" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1953230843774348</v>
+        <v>0.191349669379135</v>
       </c>
       <c r="M7" t="n">
-        <v>3.749644016819844</v>
+        <v>3.750261631266671</v>
       </c>
       <c r="N7" t="n">
-        <v>22.73851915197169</v>
+        <v>22.66986753365175</v>
       </c>
       <c r="O7" t="n">
-        <v>4.768492335316446</v>
+        <v>4.76128843210026</v>
       </c>
       <c r="P7" t="n">
-        <v>388.5692684139345</v>
+        <v>388.6253005136384</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32127,28 +32371,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2874626404838804</v>
+        <v>0.281735720783572</v>
       </c>
       <c r="J8" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1927008256925251</v>
+        <v>0.1883042866349558</v>
       </c>
       <c r="M8" t="n">
-        <v>3.477275927208264</v>
+        <v>3.476316812736641</v>
       </c>
       <c r="N8" t="n">
-        <v>21.11429492161067</v>
+        <v>21.06429712406638</v>
       </c>
       <c r="O8" t="n">
-        <v>4.595029371136889</v>
+        <v>4.58958572466692</v>
       </c>
       <c r="P8" t="n">
-        <v>389.4060153123883</v>
+        <v>389.4628833213941</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32205,28 +32449,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2232340571218459</v>
+        <v>0.2181474354256731</v>
       </c>
       <c r="J9" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K9" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1102604427531096</v>
+        <v>0.1071116636480501</v>
       </c>
       <c r="M9" t="n">
-        <v>3.950825729844428</v>
+        <v>3.945282273582206</v>
       </c>
       <c r="N9" t="n">
-        <v>24.52601004395244</v>
+        <v>24.42253310560001</v>
       </c>
       <c r="O9" t="n">
-        <v>4.952374182546431</v>
+        <v>4.941915934695775</v>
       </c>
       <c r="P9" t="n">
-        <v>388.9197283406027</v>
+        <v>388.970240960199</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32283,28 +32527,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1359190852979021</v>
+        <v>0.1312745645002319</v>
       </c>
       <c r="J10" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K10" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04330128460665805</v>
+        <v>0.04106860192357897</v>
       </c>
       <c r="M10" t="n">
-        <v>4.039795794094311</v>
+        <v>4.031980822750776</v>
       </c>
       <c r="N10" t="n">
-        <v>24.89419724448799</v>
+        <v>24.77244603762916</v>
       </c>
       <c r="O10" t="n">
-        <v>4.989408506475291</v>
+        <v>4.977192585949347</v>
       </c>
       <c r="P10" t="n">
-        <v>391.1550442803195</v>
+        <v>391.201167768746</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32361,28 +32605,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.067638812557459</v>
+        <v>0.06369448640453619</v>
       </c>
       <c r="J11" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K11" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01255917524082473</v>
+        <v>0.01131775545875535</v>
       </c>
       <c r="M11" t="n">
-        <v>3.828904608826419</v>
+        <v>3.820211046368233</v>
       </c>
       <c r="N11" t="n">
-        <v>21.93838923458436</v>
+        <v>21.81876714672927</v>
       </c>
       <c r="O11" t="n">
-        <v>4.683843425498376</v>
+        <v>4.671056320226644</v>
       </c>
       <c r="P11" t="n">
-        <v>388.270142472684</v>
+        <v>388.3093147733725</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32439,28 +32683,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.131073898601358</v>
+        <v>0.126270042638033</v>
       </c>
       <c r="J12" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K12" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0441099938506625</v>
+        <v>0.04161086655297275</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91397717445602</v>
+        <v>3.909988110461746</v>
       </c>
       <c r="N12" t="n">
-        <v>22.70733607751702</v>
+        <v>22.60819411620081</v>
       </c>
       <c r="O12" t="n">
-        <v>4.765221514002998</v>
+        <v>4.754807474146646</v>
       </c>
       <c r="P12" t="n">
-        <v>386.1694464920175</v>
+        <v>386.2171533105157</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32517,28 +32761,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1093662703990876</v>
+        <v>0.1030177499009556</v>
       </c>
       <c r="J13" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K13" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02636446829259165</v>
+        <v>0.02373981234966038</v>
       </c>
       <c r="M13" t="n">
-        <v>4.184101815766855</v>
+        <v>4.179848994211945</v>
       </c>
       <c r="N13" t="n">
-        <v>26.94058558696912</v>
+        <v>26.86844393282753</v>
       </c>
       <c r="O13" t="n">
-        <v>5.190432119483803</v>
+        <v>5.183477976496817</v>
       </c>
       <c r="P13" t="n">
-        <v>391.4283377566949</v>
+        <v>391.4913878974235</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32595,28 +32839,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1605013183654403</v>
+        <v>0.1549836545672853</v>
       </c>
       <c r="J14" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="K14" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04784229599364886</v>
+        <v>0.04535161467448956</v>
       </c>
       <c r="M14" t="n">
-        <v>4.564538693536386</v>
+        <v>4.558603134390546</v>
       </c>
       <c r="N14" t="n">
-        <v>31.26921005430147</v>
+        <v>31.128097756915</v>
       </c>
       <c r="O14" t="n">
-        <v>5.59188787926774</v>
+        <v>5.579256021811062</v>
       </c>
       <c r="P14" t="n">
-        <v>383.886133727562</v>
+        <v>383.9409275049935</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32654,7 +32898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O500"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71157,6 +71401,314 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-34.99048647246188,173.45966052575096</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-34.99106729014231,173.46015889116163</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-34.99145814527472,173.46083320914528</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-34.99172150142955,173.46161947409922</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-34.99200945787782,173.46243864108888</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-34.992281086972895,173.46326597345862</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-34.99252476245492,173.46409461069075</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-34.992721002822414,173.4649407280091</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-34.9928823167278,173.4657960941862</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-34.99300751620044,173.46665901405106</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-34.993067210585764,173.46753976653935</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>-34.99305028105182,173.46837753017877</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>-34.992879738979056,173.46920135785592</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-34.99048571229935,173.4596616100914</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-34.991066833862234,173.46015942115457</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-34.99145791250333,173.46083337663043</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-34.991718755834,173.46162086833453</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-34.99200937397202,173.46243868122417</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-34.992283201646536,173.46326502431955</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-34.99252648631294,173.46409396682677</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-34.99272222915993,173.46494036388623</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-34.992880363202026,173.46579651369493</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-34.993010119239635,173.46665871043817</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>-34.9930705440921,173.46753959823602</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>-34.99305330996458,173.46837810685997</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>-34.99287931205249,173.46920118171622</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-34.990469339565344,173.45968496511085</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-34.99105803417452,173.46016964244566</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-34.99145736937006,173.46083376742916</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-34.991716759037224,173.4616218823238</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-34.99199821449842,173.46244401921663</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-34.992279564407866,173.4632666568387</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-34.99251648793642,173.46409770123756</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-34.992718550147394,173.4649414562548</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-34.99287752170998,173.46579712388933</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-34.99301002947966,173.4666587209076</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>-34.993066219543316,173.46753981657545</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>-34.99305313179324,173.46837807293755</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>-34.99287564048399,173.46919966691462</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-34.990468345506365,173.45968638309387</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-34.991057968991655,173.4601697181589</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-34.99145178285642,173.4608377870727</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-34.99171451264085,173.46162302306166</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-34.99199385139592,173.46244610625092</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-34.992281086972895,173.46326597345862</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-34.9925155398145,173.46409805536268</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-34.99271627266342,173.4649421324829</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-34.992878942456,173.4657968187921</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-34.99300976019975,173.46665875231582</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-34.99306766105958,173.46753974379564</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>-34.99305544802065,173.46837851392905</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>-34.99287546971336,173.4691995964587</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0042/nzd0042.xlsx
+++ b/data/nzd0042/nzd0042.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26156,6 +26156,159 @@
         <v>384.71</v>
       </c>
       <c r="O504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>399.65</v>
+      </c>
+      <c r="C505" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="D505" t="n">
+        <v>395.67</v>
+      </c>
+      <c r="E505" t="n">
+        <v>395.76</v>
+      </c>
+      <c r="F505" t="n">
+        <v>395.09</v>
+      </c>
+      <c r="G505" t="n">
+        <v>392.48</v>
+      </c>
+      <c r="H505" t="n">
+        <v>393.29</v>
+      </c>
+      <c r="I505" t="n">
+        <v>390.44</v>
+      </c>
+      <c r="J505" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="K505" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="L505" t="n">
+        <v>385.58</v>
+      </c>
+      <c r="M505" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="N505" t="n">
+        <v>384.02</v>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>399.65</v>
+      </c>
+      <c r="C506" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="D506" t="n">
+        <v>396.47</v>
+      </c>
+      <c r="E506" t="n">
+        <v>396.46</v>
+      </c>
+      <c r="F506" t="n">
+        <v>395.96</v>
+      </c>
+      <c r="G506" t="n">
+        <v>392.91</v>
+      </c>
+      <c r="H506" t="n">
+        <v>393.67</v>
+      </c>
+      <c r="I506" t="n">
+        <v>390.68</v>
+      </c>
+      <c r="J506" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="K506" t="n">
+        <v>387.71</v>
+      </c>
+      <c r="L506" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="M506" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="N506" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>399.96</v>
+      </c>
+      <c r="C507" t="n">
+        <v>391.24</v>
+      </c>
+      <c r="D507" t="n">
+        <v>397.35</v>
+      </c>
+      <c r="E507" t="n">
+        <v>396.62</v>
+      </c>
+      <c r="F507" t="n">
+        <v>396.15</v>
+      </c>
+      <c r="G507" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="H507" t="n">
+        <v>394.29</v>
+      </c>
+      <c r="I507" t="n">
+        <v>391.42</v>
+      </c>
+      <c r="J507" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="K507" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="L507" t="n">
+        <v>386.12</v>
+      </c>
+      <c r="M507" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="N507" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="O507" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26172,7 +26325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B556"/>
+  <dimension ref="A1:B559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31735,6 +31888,36 @@
       </c>
       <c r="B556" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -31903,28 +32086,28 @@
         <v>0.0408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3581312927732338</v>
+        <v>0.3551820252505573</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K2" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1676824999327913</v>
+        <v>0.1670207158600101</v>
       </c>
       <c r="M2" t="n">
-        <v>4.921494360587817</v>
+        <v>4.906576211132101</v>
       </c>
       <c r="N2" t="n">
-        <v>39.19366941961626</v>
+        <v>39.0030713146898</v>
       </c>
       <c r="O2" t="n">
-        <v>6.260484759155338</v>
+        <v>6.245243895532807</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8029259480419</v>
+        <v>392.8323511735397</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31981,28 +32164,28 @@
         <v>0.0678</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2880601019176976</v>
+        <v>0.2841696189059957</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1579045148375373</v>
+        <v>0.1556493028073518</v>
       </c>
       <c r="M3" t="n">
-        <v>4.075777390681898</v>
+        <v>4.071886357068922</v>
       </c>
       <c r="N3" t="n">
-        <v>27.24351309013733</v>
+        <v>27.15588524993621</v>
       </c>
       <c r="O3" t="n">
-        <v>5.219531884195875</v>
+        <v>5.211130899328495</v>
       </c>
       <c r="P3" t="n">
-        <v>386.4776464697645</v>
+        <v>386.5164610180796</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32059,28 +32242,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3618901110296921</v>
+        <v>0.3585541235938981</v>
       </c>
       <c r="J4" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K4" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2257016338868255</v>
+        <v>0.2243589087820446</v>
       </c>
       <c r="M4" t="n">
-        <v>3.960839127732184</v>
+        <v>3.953650725803114</v>
       </c>
       <c r="N4" t="n">
-        <v>27.66031807085589</v>
+        <v>27.55243085649837</v>
       </c>
       <c r="O4" t="n">
-        <v>5.25930775586064</v>
+        <v>5.24904094635376</v>
       </c>
       <c r="P4" t="n">
-        <v>389.7964297460388</v>
+        <v>389.8297106282535</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32137,28 +32320,28 @@
         <v>0.0687</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3757831403514046</v>
+        <v>0.3713761051571911</v>
       </c>
       <c r="J5" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K5" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2605344338992297</v>
+        <v>0.257740915509593</v>
       </c>
       <c r="M5" t="n">
-        <v>3.776762291923007</v>
+        <v>3.777656399190601</v>
       </c>
       <c r="N5" t="n">
-        <v>24.67501959251341</v>
+        <v>24.62255168445541</v>
       </c>
       <c r="O5" t="n">
-        <v>4.967395654919528</v>
+        <v>4.962111615477368</v>
       </c>
       <c r="P5" t="n">
-        <v>390.1765466529969</v>
+        <v>390.2205159019817</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32215,28 +32398,28 @@
         <v>0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3600223274584813</v>
+        <v>0.3563450666361752</v>
       </c>
       <c r="J6" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K6" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2430445626259837</v>
+        <v>0.2411471752473066</v>
       </c>
       <c r="M6" t="n">
-        <v>3.909881473854861</v>
+        <v>3.904618329216976</v>
       </c>
       <c r="N6" t="n">
-        <v>24.85268825824873</v>
+        <v>24.77136085253781</v>
       </c>
       <c r="O6" t="n">
-        <v>4.985247060903675</v>
+        <v>4.977083568972677</v>
       </c>
       <c r="P6" t="n">
-        <v>389.3941600739424</v>
+        <v>389.430847720425</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32293,28 +32476,28 @@
         <v>0.0659</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2951840695622887</v>
+        <v>0.2910717159582799</v>
       </c>
       <c r="J7" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L7" t="n">
-        <v>0.191349669379135</v>
+        <v>0.1884570467112312</v>
       </c>
       <c r="M7" t="n">
-        <v>3.750261631266671</v>
+        <v>3.750100109509598</v>
       </c>
       <c r="N7" t="n">
-        <v>22.66986753365175</v>
+        <v>22.61685068920324</v>
       </c>
       <c r="O7" t="n">
-        <v>4.76128843210026</v>
+        <v>4.75571768392566</v>
       </c>
       <c r="P7" t="n">
-        <v>388.6253005136384</v>
+        <v>388.666329929317</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32371,28 +32554,28 @@
         <v>0.0668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.281735720783572</v>
+        <v>0.2781141576902274</v>
       </c>
       <c r="J8" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K8" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1883042866349558</v>
+        <v>0.1858621079826123</v>
       </c>
       <c r="M8" t="n">
-        <v>3.476316812736641</v>
+        <v>3.472531395255787</v>
       </c>
       <c r="N8" t="n">
-        <v>21.06429712406638</v>
+        <v>21.00323993780583</v>
       </c>
       <c r="O8" t="n">
-        <v>4.58958572466692</v>
+        <v>4.582929187518156</v>
       </c>
       <c r="P8" t="n">
-        <v>389.4628833213941</v>
+        <v>389.4990148513901</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32449,28 +32632,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2181474354256731</v>
+        <v>0.2137506904747959</v>
       </c>
       <c r="J9" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K9" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1071116636480501</v>
+        <v>0.1041165665119748</v>
       </c>
       <c r="M9" t="n">
-        <v>3.945282273582206</v>
+        <v>3.943922541756447</v>
       </c>
       <c r="N9" t="n">
-        <v>24.42253310560001</v>
+        <v>24.37135686924496</v>
       </c>
       <c r="O9" t="n">
-        <v>4.941915934695775</v>
+        <v>4.9367354465522</v>
       </c>
       <c r="P9" t="n">
-        <v>388.970240960199</v>
+        <v>389.0141066905517</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32527,28 +32710,28 @@
         <v>0.0581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1312745645002319</v>
+        <v>0.1270052651042297</v>
       </c>
       <c r="J10" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K10" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04106860192357897</v>
+        <v>0.03888816679267526</v>
       </c>
       <c r="M10" t="n">
-        <v>4.031980822750776</v>
+        <v>4.030138235878602</v>
       </c>
       <c r="N10" t="n">
-        <v>24.77244603762916</v>
+        <v>24.71342243462301</v>
       </c>
       <c r="O10" t="n">
-        <v>4.977192585949347</v>
+        <v>4.971259642648231</v>
       </c>
       <c r="P10" t="n">
-        <v>391.201167768746</v>
+        <v>391.2437627969251</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32605,28 +32788,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06369448640453619</v>
+        <v>0.0608393780590499</v>
       </c>
       <c r="J11" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K11" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01131775545875535</v>
+        <v>0.01044946875600994</v>
       </c>
       <c r="M11" t="n">
-        <v>3.820211046368233</v>
+        <v>3.813079570048223</v>
       </c>
       <c r="N11" t="n">
-        <v>21.81876714672927</v>
+        <v>21.72932744936831</v>
       </c>
       <c r="O11" t="n">
-        <v>4.671056320226644</v>
+        <v>4.661472669593625</v>
       </c>
       <c r="P11" t="n">
-        <v>388.3093147733725</v>
+        <v>388.3378000811127</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32683,28 +32866,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.126270042638033</v>
+        <v>0.122291039985362</v>
       </c>
       <c r="J12" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K12" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04161086655297275</v>
+        <v>0.03948825008826629</v>
       </c>
       <c r="M12" t="n">
-        <v>3.909988110461746</v>
+        <v>3.908953835026031</v>
       </c>
       <c r="N12" t="n">
-        <v>22.60819411620081</v>
+        <v>22.55054584534283</v>
       </c>
       <c r="O12" t="n">
-        <v>4.754807474146646</v>
+        <v>4.748741501213014</v>
       </c>
       <c r="P12" t="n">
-        <v>386.2171533105157</v>
+        <v>386.2568527516358</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32761,28 +32944,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1030177499009556</v>
+        <v>0.09989303473086071</v>
       </c>
       <c r="J13" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K13" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02373981234966038</v>
+        <v>0.02259518384100578</v>
       </c>
       <c r="M13" t="n">
-        <v>4.179848994211945</v>
+        <v>4.169204983158441</v>
       </c>
       <c r="N13" t="n">
-        <v>26.86844393282753</v>
+        <v>26.75851439603164</v>
       </c>
       <c r="O13" t="n">
-        <v>5.183477976496817</v>
+        <v>5.172863268638718</v>
       </c>
       <c r="P13" t="n">
-        <v>391.4913878974235</v>
+        <v>391.5225641956126</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32839,28 +33022,28 @@
         <v>0.1633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1549836545672853</v>
+        <v>0.1516572100122073</v>
       </c>
       <c r="J14" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="K14" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04535161467448956</v>
+        <v>0.04397105416414193</v>
       </c>
       <c r="M14" t="n">
-        <v>4.558603134390546</v>
+        <v>4.549775710082784</v>
       </c>
       <c r="N14" t="n">
-        <v>31.128097756915</v>
+        <v>31.00011300426061</v>
       </c>
       <c r="O14" t="n">
-        <v>5.579256021811062</v>
+        <v>5.567774510902953</v>
       </c>
       <c r="P14" t="n">
-        <v>383.9409275049935</v>
+        <v>383.9741134719744</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32898,7 +33081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71709,6 +71892,237 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-34.990473783593586,173.4596786258922</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-34.99106963672554,173.4601561654836</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-34.99144503248559,173.46084264414134</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-34.99171858943427,173.46162095283364</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-34.991999053556604,173.46244361786387</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-34.992284132102945,173.46326460669837</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-34.99252045280988,173.46409622035063</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-34.992728536038555,173.46493849125423</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-34.99289048601743,173.46579433987688</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-34.99301415843838,173.46665823931468</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-34.99307567949377,173.4675393389579</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>-34.99304814299575,173.46837712310972</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>-34.9928813613,173.46920202718692</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-34.990473783593586,173.4596786258922</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-34.991064943559024,173.46016161683949</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-34.991438825247876,173.46084711041058</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-34.991712765443644,173.46162391030222</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-34.991991753750455,173.46244710963268</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-34.99228049486427,173.46326623921755</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-34.99251717747962,173.46409744369203</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-34.99272643374569,173.46493911546494</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-34.992886490169255,173.465795197963</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-34.99300679812067,173.4666590978063</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-34.99306910257585,173.46753967101583</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>-34.99303362203155,173.468374358433</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>-34.992869407356054,173.469197095275</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-34.99047197089791,173.45968121162622</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-34.99106194514695,173.46016509964988</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-34.991431997286206,173.460852023306</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-34.99171143424577,173.46162458629496</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-34.9919901595399,173.4624478722028</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-34.992278887712295,173.46326696056317</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-34.99251183351973,173.4640994396699</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-34.99271995167598,173.46494104011438</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>-34.99288391506708,173.4657957509518</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-34.993006977640604,173.4666590768675</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-34.99307081437639,173.4675395845898</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-34.99304137248483,173.4683758340579</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>-34.99286590655814,173.46919565092966</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
